--- a/excel/output_class.xlsx
+++ b/excel/output_class.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>(0, 5.25)</t>
+          <t>(0, 5.25, 0)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>(0, 1.01)</t>
+          <t>(0, 1.01, 0)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>(0, 3.34)</t>
+          <t>(0, 3.34, 0)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>(0, 5.28)</t>
+          <t>(0, 5.28, 0)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(0, 3.4)</t>
+          <t>(0, 3.4, 0)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>(0, 5.25)</t>
+          <t>(0, 5.25, 0)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>(0, 4.1)</t>
+          <t>(0, 4.1, 0)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>(0, 0.52)</t>
+          <t>(0, 0.52, 0)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>(0, 3.3)</t>
+          <t>(0, 3.3, 0)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>(0, 6.3)</t>
+          <t>(0, 6.3, 0)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>(0, 32.4)</t>
+          <t>(0, 32.4, 0)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>(0, 5.0)</t>
+          <t>(0, 5.0, 0)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>(0, 3.0)</t>
+          <t>(0, 3.0, 0)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>(0, 30.0)</t>
+          <t>(0, 30.0, 0)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>(0, 4.4)</t>
+          <t>(0, 4.4, 0)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>(0, 20.2)</t>
+          <t>(0, 20.2, 0)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>(0, 30.3)</t>
+          <t>(0, 30.3, 0)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>(0, 10.5)</t>
+          <t>(0, 10.5, 0)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>(0, 8.3)</t>
+          <t>(0, 8.3, 0)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>(0, 12.2)</t>
+          <t>(0, 12.2, 0)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>(0, 21.0)</t>
+          <t>(0, 21.0, 0)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>(0, 3.1)</t>
+          <t>(0, 3.1, 0)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>(0, 5.0)</t>
+          <t>(0, 5.0, 0)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>(0, 1.05)</t>
+          <t>(0, 1.05, 0)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>(0, 4.4)</t>
+          <t>(0, 4.4, 0)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>(0, 4.2)</t>
+          <t>(0, 4.2, 0)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>(0, 9.3)</t>
+          <t>(0, 9.3, 0)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>(0, 15.5)</t>
+          <t>(0, 15.5, 0)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>(0, 3.3)</t>
+          <t>(0, 3.3, 0)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>(0, 4.4)</t>
+          <t>(0, 4.4, 0)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>(0, 20.0)</t>
+          <t>(0, 20.0, 0)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>(0, 7.8)</t>
+          <t>(0, 7.8, 0)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>(0, 10.4)</t>
+          <t>(0, 10.4, 0)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>(0, 8.0)</t>
+          <t>(0, 8.0, 0)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>(0, 19.6)</t>
+          <t>(0, 19.6, 0)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>(0, 35.18)</t>
+          <t>(0, 35.18, 0)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>(0, 3.23)</t>
+          <t>(0, 3.23, 0)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>(0, 41.7)</t>
+          <t>(0, 41.7, 0)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>(0, 3.2)</t>
+          <t>(0, 3.2, 0)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>(0, 6.2)</t>
+          <t>(0, 6.2, 0)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>(0, 30.2)</t>
+          <t>(0, 30.2, 0)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>(0, 3.3)</t>
+          <t>(0, 3.3, 0)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>(0, 36.3)</t>
+          <t>(0, 36.3, 0)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>(0, 3.1)</t>
+          <t>(0, 3.1, 0)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>(0, 16.68)</t>
+          <t>(0, 16.68, 0)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>(0, 13.2)</t>
+          <t>(0, 13.2, 0)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>(0, 5.25)</t>
+          <t>(0, 5.25, 0)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>(0, 4.4)</t>
+          <t>(0, 4.4, 0)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>(0, 4.8)</t>
+          <t>(0, 4.8, 0)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>(0, 1.7)</t>
+          <t>(0, 1.7, 0)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>(0, 5.2)</t>
+          <t>(0, 5.2, 0)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>(0, 2.4)</t>
+          <t>(0, 2.4, 0)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>(0, 5.1)</t>
+          <t>(0, 5.1, 0)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>(0, 3.3)</t>
+          <t>(0, 3.3, 0)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>(0, 1.1)</t>
+          <t>(0, 1.1, 0)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>(0, 4.4)</t>
+          <t>(0, 4.4, 0)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>(0, 2.2)</t>
+          <t>(0, 2.2, 0)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>(0, 6.4)</t>
+          <t>(0, 6.4, 0)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>(0, 10.5)</t>
+          <t>(0, 10.5, 0)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>(0, 2.55)</t>
+          <t>(0, 2.55, 0)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>(0, 2.55)</t>
+          <t>(0, 2.55, 0)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>(0, 8.2)</t>
+          <t>(0, 8.2, 0)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>(0, 10.2)</t>
+          <t>(0, 10.2, 0)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>(0, 5.0)</t>
+          <t>(0, 5.0, 0)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>(0, 10.0)</t>
+          <t>(0, 10.0, 0)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>(0, 12.5)</t>
+          <t>(0, 12.5, 0)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>(0, 7.5)</t>
+          <t>(0, 7.5, 0)</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>(0, 5.5)</t>
+          <t>(0, 5.5, 0)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>(0, 2.55)</t>
+          <t>(0, 2.55, 0)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>(0, 5.5)</t>
+          <t>(0, 5.5, 0)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>(0, 3.55)</t>
+          <t>(0, 3.55, 0)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>(0, 12.75)</t>
+          <t>(0, 12.75, 0)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>(0, 14.3)</t>
+          <t>(0, 14.3, 0)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>(0, 23.5)</t>
+          <t>(0, 23.5, 0)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>(0, 12.5)</t>
+          <t>(0, 12.5, 0)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>(0, 2.55)</t>
+          <t>(0, 2.55, 0)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>(0, 4.2)</t>
+          <t>(0, 4.2, 0)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>(0, 2.21)</t>
+          <t>(0, 2.21, 0)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>(0, 30.45)</t>
+          <t>(0, 30.45, 0)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>(0, 10.32)</t>
+          <t>(0, 10.32, 0)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>(0, 2.5)</t>
+          <t>(0, 2.5, 0)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>(0, 9.6)</t>
+          <t>(0, 9.6, 0)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>(0, 4.08)</t>
+          <t>(0, 4.08, 0)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>(0, 8.64)</t>
+          <t>(0, 8.64, 0)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>(0, 3.24)</t>
+          <t>(0, 3.24, 0)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>(0, 5.2)</t>
+          <t>(0, 5.2, 0)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>(0, 2.24)</t>
+          <t>(0, 2.24, 0)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>(0, 1.6)</t>
+          <t>(0, 1.6, 0)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>(0, 1.6)</t>
+          <t>(0, 1.6, 0)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>(0, 2.65)</t>
+          <t>(0, 2.65, 0)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>(0, 1.57)</t>
+          <t>(0, 1.57, 0)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>(0, 6.3)</t>
+          <t>(0, 6.3, 0)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>(0, 10.5)</t>
+          <t>(0, 10.5, 0)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>(0, 4.27)</t>
+          <t>(0, 4.27, 0)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7047,7 +7047,7 @@
         <v>45241</v>
       </c>
       <c r="E152" t="n">
-        <v>0.215</v>
+        <v>38.6</v>
       </c>
       <c r="F152" t="n">
         <v>38.39</v>
@@ -7056,11 +7056,11 @@
         <v>39.09</v>
       </c>
       <c r="H152" t="n">
-        <v>4.3</v>
+        <v>772</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>(0, 4.3)</t>
+          <t>(20, 4.2, 1)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7093,7 +7093,7 @@
         <v>45249</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2</v>
+        <v>38.59</v>
       </c>
       <c r="F153" t="n">
         <v>38.39</v>
@@ -7102,11 +7102,11 @@
         <v>166.67</v>
       </c>
       <c r="H153" t="n">
-        <v>20</v>
+        <v>3859</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>(0, 20.0)</t>
+          <t>(100, 20.0, 1)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -7139,7 +7139,7 @@
         <v>45250</v>
       </c>
       <c r="E154" t="n">
-        <v>0.37</v>
+        <v>38.4</v>
       </c>
       <c r="F154" t="n">
         <v>38.39</v>
@@ -7148,11 +7148,11 @@
         <v>185</v>
       </c>
       <c r="H154" t="n">
-        <v>22.2</v>
+        <v>2304</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>(0, 22.2)</t>
+          <t>(60, 0.6, 1)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>(0, 15.3)</t>
+          <t>(0, 15.3, 0)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>(0, 10.2)</t>
+          <t>(0, 10.2, 0)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>(0, 9.3)</t>
+          <t>(0, 9.3, 0)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>(0, 10.2)</t>
+          <t>(0, 10.2, 0)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>(0, 40.8)</t>
+          <t>(0, 40.8, 0)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>(0, 10.5)</t>
+          <t>(0, 10.5, 0)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>(0, 20.4)</t>
+          <t>(0, 20.4, 0)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>(0, 10.2)</t>
+          <t>(0, 10.2, 0)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>(0, 6.2)</t>
+          <t>(0, 6.2, 0)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>(0, 14.2)</t>
+          <t>(0, 14.2, 0)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>(0, 3.3)</t>
+          <t>(0, 3.3, 0)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>(0, 15.3)</t>
+          <t>(0, 15.3, 0)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>(0, 8.4)</t>
+          <t>(0, 8.4, 0)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>(0, 20.4)</t>
+          <t>(0, 20.4, 0)</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>(0, 30.6)</t>
+          <t>(0, 30.6, 0)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>(0, 1.5)</t>
+          <t>(0, 1.5, 0)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>(0, 20.4)</t>
+          <t>(0, 20.4, 0)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>(0, 6.2)</t>
+          <t>(0, 6.2, 0)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>(0, 20.2)</t>
+          <t>(0, 20.2, 0)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>(0, 15.3)</t>
+          <t>(0, 15.3, 0)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>(0, 14.0)</t>
+          <t>(0, 14.0, 0)</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>(0, 4.0)</t>
+          <t>(0, 4.0, 0)</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>(0, 17.5)</t>
+          <t>(0, 17.5, 0)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>(0, 3.57)</t>
+          <t>(0, 3.57, 0)</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>(0, 3.57)</t>
+          <t>(0, 3.57, 0)</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>(0, 1.5)</t>
+          <t>(0, 1.5, 0)</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>(0, 10.0)</t>
+          <t>(0, 10.0, 0)</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>(0, 20.0)</t>
+          <t>(0, 20.0, 0)</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>(0, 12.5)</t>
+          <t>(0, 12.5, 0)</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>(0, 10.0)</t>
+          <t>(0, 10.0, 0)</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>(0, 2.1)</t>
+          <t>(0, 2.1, 0)</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>(0, 2.24)</t>
+          <t>(0, 2.24, 0)</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>(0, 2.24)</t>
+          <t>(0, 2.24, 0)</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -8843,7 +8843,7 @@
         <v>45258</v>
       </c>
       <c r="E193" t="n">
-        <v>0.52</v>
+        <v>60.52</v>
       </c>
       <c r="F193" t="n">
         <v>38.39</v>
@@ -8852,11 +8852,11 @@
         <v>17.33</v>
       </c>
       <c r="H193" t="n">
-        <v>2.6</v>
+        <v>302.6</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>(0, 2.6)</t>
+          <t>(7, 33.87, 1)</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>(0, 1.6)</t>
+          <t>(0, 1.6, 0)</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -8935,7 +8935,7 @@
         <v>45258</v>
       </c>
       <c r="E195" t="n">
-        <v>0.36</v>
+        <v>39.36</v>
       </c>
       <c r="F195" t="n">
         <v>38.39</v>
@@ -8944,11 +8944,11 @@
         <v>48</v>
       </c>
       <c r="H195" t="n">
-        <v>7.2</v>
+        <v>787.2</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>(0, 7.2)</t>
+          <t>(20, 19.4, 1)</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -8981,7 +8981,7 @@
         <v>45258</v>
       </c>
       <c r="E196" t="n">
-        <v>0.54</v>
+        <v>38.54</v>
       </c>
       <c r="F196" t="n">
         <v>38.39</v>
@@ -8990,11 +8990,11 @@
         <v>100.8</v>
       </c>
       <c r="H196" t="n">
-        <v>15.12</v>
+        <v>1079.12</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>(0, 15.12)</t>
+          <t>(28, 4.2, 1)</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>(1, 19.67)</t>
+          <t>(1, 19.67, 1)</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>(0, 20.0)</t>
+          <t>(0, 20.0, 0)</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>(0, 1.4)</t>
+          <t>(0, 1.4, 0)</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>(0, 2.0)</t>
+          <t>(0, 2.0, 0)</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>(0, 1.5)</t>
+          <t>(0, 1.5, 0)</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>(0, 20.24)</t>
+          <t>(0, 20.24, 0)</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>(0, 14.5)</t>
+          <t>(0, 14.5, 0)</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>(8, 20.57)</t>
+          <t>(8, 20.57, 1)</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>(6, 6.55)</t>
+          <t>(6, 6.55, 1)</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>(2, 44.94)</t>
+          <t>(2, 44.94, 1)</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>(0, 14.4)</t>
+          <t>(0, 14.4, 0)</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>(0, 4.38)</t>
+          <t>(0, 4.38, 0)</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>(0, 83.4)</t>
+          <t>(0, 83.4, 0)</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>(0, 50.1)</t>
+          <t>(0, 50.1, 0)</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>(1, 50.38)</t>
+          <t>(1, 50.38, 1)</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>(3, 8.43)</t>
+          <t>(3, 8.43, 1)</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>(0, 1.0)</t>
+          <t>(0, 1.0, 0)</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
